--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="61">
   <si>
     <t>Profile</t>
   </si>
@@ -68,63 +68,60 @@
     <t>dateTimeĵ, Periodĵ</t>
   </si>
   <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>mesures-fr-observation-body-temperature</t>
+  </si>
+  <si>
+    <t>Température</t>
+  </si>
+  <si>
+    <t>null#8310-5</t>
+  </si>
+  <si>
+    <t>mesures-fr-observation-body-weight</t>
+  </si>
+  <si>
+    <t>Poids</t>
+  </si>
+  <si>
+    <t>null#29463-7</t>
+  </si>
+  <si>
+    <t>mesures-fr-observation-bodyheight</t>
+  </si>
+  <si>
+    <t>Taille</t>
+  </si>
+  <si>
+    <t>null#8302-2</t>
+  </si>
+  <si>
+    <t>mesures-fr-observation-bp</t>
+  </si>
+  <si>
+    <t>Pression Artérielle</t>
+  </si>
+  <si>
+    <t>null#85354-9</t>
+  </si>
+  <si>
+    <t>dateTimeĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>mesures-fr-observation-body-temperature</t>
-  </si>
-  <si>
-    <t>Température</t>
-  </si>
-  <si>
-    <t>null#8310-5</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
-    <t>mesures-fr-observation-body-weight</t>
-  </si>
-  <si>
-    <t>Poids</t>
-  </si>
-  <si>
-    <t>null#29463-7</t>
-  </si>
-  <si>
-    <t>mesures-fr-observation-bodyheight</t>
-  </si>
-  <si>
-    <t>Taille</t>
-  </si>
-  <si>
-    <t>null#8302-2</t>
-  </si>
-  <si>
-    <t>mesures-fr-observation-bp</t>
-  </si>
-  <si>
-    <t>Pression Artérielle</t>
-  </si>
-  <si>
-    <t>null#85354-9</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
-  </si>
-  <si>
     <t>LOINC#8478-0</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS (extensible)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ</t>
   </si>
   <si>
     <t>mesures-observation-head-circumference</t>
@@ -430,7 +424,7 @@
         <v>17</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>19</v>
@@ -444,19 +438,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>26</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>16</v>
@@ -465,7 +459,7 @@
         <v>17</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>19</v>
@@ -479,19 +473,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>29</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>16</v>
@@ -500,7 +494,7 @@
         <v>17</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>19</v>
@@ -514,25 +508,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="C6" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s" s="2">
+      <c r="F6" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>33</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>14</v>
@@ -552,7 +546,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>14</v>
@@ -579,7 +573,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +581,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>14</v>
@@ -614,7 +608,7 @@
         <v>14</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -622,7 +616,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>14</v>
@@ -640,33 +634,33 @@
         <v>14</v>
       </c>
       <c r="H9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>40</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>16</v>
@@ -675,7 +669,7 @@
         <v>17</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>19</v>
@@ -689,19 +683,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>43</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>16</v>
@@ -724,19 +718,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>46</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>16</v>
@@ -759,28 +753,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>49</v>
-      </c>
       <c r="G13" t="s" s="2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>19</v>
@@ -794,19 +788,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>16</v>
@@ -815,7 +809,7 @@
         <v>17</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>19</v>
@@ -829,28 +823,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>56</v>
-      </c>
       <c r="F15" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>19</v>
@@ -864,19 +858,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>16</v>
@@ -885,7 +879,7 @@
         <v>17</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>19</v>
@@ -899,19 +893,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>16</v>
@@ -920,7 +914,7 @@
         <v>17</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>19</v>

--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
   <si>
     <t>Profile</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>null#8287-5</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
   </si>
   <si>
     <t>mesures-observation-pain-severity</t>
@@ -803,7 +806,7 @@
         <v>51</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>17</v>
@@ -823,22 +826,22 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>32</v>
@@ -858,10 +861,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -870,10 +873,10 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>17</v>
@@ -893,10 +896,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -905,10 +908,10 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>17</v>

--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
   <si>
     <t>Profile</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Indice de Masse Corporelle</t>
   </si>
   <si>
-    <t>null#vital-signs</t>
+    <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
     <t/>
@@ -152,6 +152,60 @@
     <t>null#9279-1</t>
   </si>
   <si>
+    <t>mesures-observation-cholesterol-aspect</t>
+  </si>
+  <si>
+    <t>Cholestérol - aspect</t>
+  </si>
+  <si>
+    <t>LOINC#11158-3</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-hdl</t>
+  </si>
+  <si>
+    <t>Cholestérol - HDL</t>
+  </si>
+  <si>
+    <t>LOINC#2085-9</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-ldl</t>
+  </si>
+  <si>
+    <t>Cholestérol - LDL</t>
+  </si>
+  <si>
+    <t>LOINC#2089-1</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-total</t>
+  </si>
+  <si>
+    <t>Cholestérol - total</t>
+  </si>
+  <si>
+    <t>LOINC#2093-3</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-trigly</t>
+  </si>
+  <si>
+    <t>Cholestérol - triglycerides</t>
+  </si>
+  <si>
+    <t>LOINC#2571-8</t>
+  </si>
+  <si>
     <t>mesures-observation-glucose</t>
   </si>
   <si>
@@ -161,16 +215,25 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS (extensible)</t>
   </si>
   <si>
+    <t>mesures-observation-hb1ac</t>
+  </si>
+  <si>
+    <t>Hémoglobine glyquée (Hb1Ac)</t>
+  </si>
+  <si>
+    <t>null#4548-4</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
+  </si>
+  <si>
     <t>mesures-observation-head-circumference</t>
   </si>
   <si>
     <t>Périmètre Crânien</t>
   </si>
   <si>
-    <t>null#8287-5</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
+    <t>null#9843-4, null#8287-5</t>
   </si>
   <si>
     <t>mesures-observation-pain-severity</t>
@@ -331,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -762,22 +825,22 @@
         <v>47</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>19</v>
@@ -791,28 +854,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="F14" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>17</v>
-      </c>
       <c r="H14" t="s" s="2">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>19</v>
@@ -826,28 +889,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>19</v>
@@ -861,28 +924,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>19</v>
@@ -896,36 +959,246 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K17" t="s" s="2">
+      <c r="H20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>14</v>
       </c>
     </row>
